--- a/informed_consent_forms/020_homeless_outreach_data_protection_consent_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/020_homeless_outreach_data_protection_consent_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -866,8 +866,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -895,12 +895,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'homeless_outreach_team',_'value':_'homeless_outreach_team'}</t>
+          <t>homeless_outreach_team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Homeless Outreach Team', 'value': 'Homeless Outreach Team'}</t>
+          <t>Homeless Outreach Team</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'another_team',_'value':_'another_team'}</t>
+          <t>another_team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Another team', 'value': 'Another team'}</t>
+          <t>Another team</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'calls',_'value':_'calls'}</t>
+          <t>calls</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Calls', 'value': 'Calls'}</t>
+          <t>Calls</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'texts',_'value':_'texts'}</t>
+          <t>texts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Texts', 'value': 'Texts'}</t>
+          <t>Texts</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'emails',_'value':_'emails'}</t>
+          <t>emails</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Emails', 'value': 'Emails'}</t>
+          <t>Emails</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'contact_info',_'value':_'contact_info'}</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Contact info', 'value': 'contact_info'}</t>
+          <t>Contact info</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'follow-up',_'value':_'follow_up'}</t>
+          <t>follow-up</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Follow-up', 'value': 'follow_up'}</t>
+          <t>Follow-up</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'demographics',_'value':_'demographics'}</t>
+          <t>demographics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Demographics', 'value': 'demographics'}</t>
+          <t>Demographics</t>
         </is>
       </c>
     </row>
